--- a/artfynd/A 43261-2021 artfynd.xlsx
+++ b/artfynd/A 43261-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43261-2021 artfynd.xlsx
+++ b/artfynd/A 43261-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3477,37 +3477,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112606174</v>
+        <v>112606177</v>
       </c>
       <c r="B26" t="n">
-        <v>77856</v>
+        <v>57372</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>720984</v>
+        <v>720975</v>
       </c>
       <c r="R26" t="n">
-        <v>7146655</v>
+        <v>7146776</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3584,10 +3584,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112606164</v>
+        <v>112610224</v>
       </c>
       <c r="B27" t="n">
-        <v>77856</v>
+        <v>77891</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3600,21 +3600,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3624,10 +3624,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721087</v>
+        <v>721095</v>
       </c>
       <c r="R27" t="n">
-        <v>7146610</v>
+        <v>7146589</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112606167</v>
+        <v>112610223</v>
       </c>
       <c r="B28" t="n">
-        <v>78448</v>
+        <v>56623</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>721097</v>
+        <v>721119</v>
       </c>
       <c r="R28" t="n">
-        <v>7146590</v>
+        <v>7146624</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3798,7 +3798,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112606177</v>
+        <v>112610230</v>
       </c>
       <c r="B29" t="n">
         <v>57372</v>
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720975</v>
+        <v>720972</v>
       </c>
       <c r="R29" t="n">
-        <v>7146776</v>
+        <v>7146771</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3905,10 +3905,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112606171</v>
+        <v>112610226</v>
       </c>
       <c r="B30" t="n">
-        <v>77856</v>
+        <v>77891</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3921,21 +3921,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720936</v>
+        <v>720911</v>
       </c>
       <c r="R30" t="n">
-        <v>7146562</v>
+        <v>7146621</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4012,10 +4012,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112606176</v>
+        <v>112610227</v>
       </c>
       <c r="B31" t="n">
-        <v>5160</v>
+        <v>77608</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4024,25 +4024,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720995</v>
+        <v>720959</v>
       </c>
       <c r="R31" t="n">
-        <v>7146704</v>
+        <v>7146664</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4119,10 +4119,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112606166</v>
+        <v>112610229</v>
       </c>
       <c r="B32" t="n">
-        <v>77891</v>
+        <v>5160</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4131,25 +4131,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>721099</v>
+        <v>720991</v>
       </c>
       <c r="R32" t="n">
-        <v>7146591</v>
+        <v>7146705</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4226,7 +4226,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112606181</v>
+        <v>112610233</v>
       </c>
       <c r="B33" t="n">
         <v>77856</v>
@@ -4266,10 +4266,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>721050</v>
+        <v>721051</v>
       </c>
       <c r="R33" t="n">
-        <v>7146812</v>
+        <v>7146813</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4330,1611 +4330,6 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>112610224</v>
-      </c>
-      <c r="B34" t="n">
-        <v>77891</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>185</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Bryoria nadvornikiana</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>721095</v>
-      </c>
-      <c r="R34" t="n">
-        <v>7146589</v>
-      </c>
-      <c r="S34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>112610223</v>
-      </c>
-      <c r="B35" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>721119</v>
-      </c>
-      <c r="R35" t="n">
-        <v>7146624</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>112606173</v>
-      </c>
-      <c r="B36" t="n">
-        <v>77608</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>720961</v>
-      </c>
-      <c r="R36" t="n">
-        <v>7146659</v>
-      </c>
-      <c r="S36" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>112606182</v>
-      </c>
-      <c r="B37" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>721076</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7146751</v>
-      </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>112606168</v>
-      </c>
-      <c r="B38" t="n">
-        <v>5160</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>720868</v>
-      </c>
-      <c r="R38" t="n">
-        <v>7146633</v>
-      </c>
-      <c r="S38" t="n">
-        <v>10</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>112610230</v>
-      </c>
-      <c r="B39" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Perisoreus infaustus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>720972</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7146771</v>
-      </c>
-      <c r="S39" t="n">
-        <v>10</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>112610226</v>
-      </c>
-      <c r="B40" t="n">
-        <v>77891</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>185</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Bryoria nadvornikiana</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>720911</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7146621</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>112610228</v>
-      </c>
-      <c r="B41" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>720985</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7146655</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>112606170</v>
-      </c>
-      <c r="B42" t="n">
-        <v>5160</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>720939</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7146566</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>112610227</v>
-      </c>
-      <c r="B43" t="n">
-        <v>77608</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>720959</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7146664</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>112606179</v>
-      </c>
-      <c r="B44" t="n">
-        <v>5160</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>720958</v>
-      </c>
-      <c r="R44" t="n">
-        <v>7146897</v>
-      </c>
-      <c r="S44" t="n">
-        <v>10</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>112606169</v>
-      </c>
-      <c r="B45" t="n">
-        <v>77891</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>185</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Bryoria nadvornikiana</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>720912</v>
-      </c>
-      <c r="R45" t="n">
-        <v>7146618</v>
-      </c>
-      <c r="S45" t="n">
-        <v>10</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>112610229</v>
-      </c>
-      <c r="B46" t="n">
-        <v>5160</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>720991</v>
-      </c>
-      <c r="R46" t="n">
-        <v>7146705</v>
-      </c>
-      <c r="S46" t="n">
-        <v>10</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>112610233</v>
-      </c>
-      <c r="B47" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>721051</v>
-      </c>
-      <c r="R47" t="n">
-        <v>7146813</v>
-      </c>
-      <c r="S47" t="n">
-        <v>10</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>112606165</v>
-      </c>
-      <c r="B48" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>721121</v>
-      </c>
-      <c r="R48" t="n">
-        <v>7146627</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43261-2021 artfynd.xlsx
+++ b/artfynd/A 43261-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104159450</v>
+        <v>112606166</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721050.2409451447</v>
+        <v>721099</v>
       </c>
       <c r="R2" t="n">
-        <v>7146811.661621775</v>
+        <v>7146590</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,14 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104159451</v>
+        <v>112606169</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721075.9372297983</v>
+        <v>720911</v>
       </c>
       <c r="R3" t="n">
-        <v>7146750.975562354</v>
+        <v>7146618</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,24 +845,14 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104159436</v>
+        <v>112610224</v>
       </c>
       <c r="B4" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721096.7372237599</v>
+        <v>721095</v>
       </c>
       <c r="R4" t="n">
-        <v>7146589.599022079</v>
+        <v>7146590</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,24 +947,14 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,37 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104159437</v>
+        <v>112610226</v>
       </c>
       <c r="B5" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720868.3509935506</v>
+        <v>720912</v>
       </c>
       <c r="R5" t="n">
-        <v>7146632.601727481</v>
+        <v>7146621</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,24 +1049,14 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,37 +1083,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104159435</v>
+        <v>112606164</v>
       </c>
       <c r="B6" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>721098.8379681882</v>
+        <v>721086</v>
       </c>
       <c r="R6" t="n">
-        <v>7146590.619622697</v>
+        <v>7146610</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,24 +1151,14 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,19 +1185,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104159444</v>
+        <v>112606171</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1293,21 +1213,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gladaberg, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720984.1640916736</v>
+        <v>720936</v>
       </c>
       <c r="R7" t="n">
-        <v>7146654.867756982</v>
+        <v>7146562</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,24 +1253,14 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,37 +1287,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104159440</v>
+        <v>112606174</v>
       </c>
       <c r="B8" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1421,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720939.2941794335</v>
+        <v>720984</v>
       </c>
       <c r="R8" t="n">
-        <v>7146565.623737742</v>
+        <v>7146655</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,24 +1355,14 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,37 +1389,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104159438</v>
+        <v>112606181</v>
       </c>
       <c r="B9" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1538,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720911.5967037941</v>
+        <v>721050</v>
       </c>
       <c r="R9" t="n">
-        <v>7146617.91714772</v>
+        <v>7146812</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,24 +1457,14 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,19 +1491,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104159433</v>
+        <v>112606182</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1655,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721086.5536017686</v>
+        <v>721076</v>
       </c>
       <c r="R10" t="n">
-        <v>7146610.146289532</v>
+        <v>7146751</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,24 +1559,14 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,19 +1593,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104159442</v>
+        <v>112610228</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1772,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720936.0515171493</v>
+        <v>720985</v>
       </c>
       <c r="R11" t="n">
-        <v>7146562.348953938</v>
+        <v>7146655</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1805,24 +1661,14 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1849,37 +1695,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104159434</v>
+        <v>112610231</v>
       </c>
       <c r="B12" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1889,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721120.5665631434</v>
+        <v>720880</v>
       </c>
       <c r="R12" t="n">
-        <v>7146626.939219442</v>
+        <v>7146831</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1922,24 +1763,14 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,37 +1797,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104159446</v>
+        <v>112610233</v>
       </c>
       <c r="B13" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2006,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720995.3763269221</v>
+        <v>721051</v>
       </c>
       <c r="R13" t="n">
-        <v>7146704.324563822</v>
+        <v>7146813</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2039,24 +1865,14 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2083,15 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104159443</v>
+        <v>112606173</v>
       </c>
       <c r="B14" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2123,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720960.8285169172</v>
+        <v>720961</v>
       </c>
       <c r="R14" t="n">
-        <v>7146658.828028596</v>
+        <v>7146659</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2156,24 +1967,14 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2200,37 +2001,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104159448</v>
+        <v>112610227</v>
       </c>
       <c r="B15" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2240,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720957.9955514764</v>
+        <v>720959</v>
       </c>
       <c r="R15" t="n">
-        <v>7146896.635966301</v>
+        <v>7146664</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2273,24 +2069,14 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2317,37 +2103,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>109909842</v>
+        <v>112606167</v>
       </c>
       <c r="B16" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2357,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720971.4385826343</v>
+        <v>721097</v>
       </c>
       <c r="R16" t="n">
-        <v>7146770.785394685</v>
+        <v>7146589</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2390,19 +2171,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2434,15 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>109909841</v>
+        <v>112610225</v>
       </c>
       <c r="B17" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,21 +2216,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2474,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720991.4202166767</v>
+        <v>721097</v>
       </c>
       <c r="R17" t="n">
-        <v>7146704.907342575</v>
+        <v>7146591</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2507,19 +2273,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2551,15 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>109909845</v>
+        <v>112606165</v>
       </c>
       <c r="B18" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2567,21 +2318,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2591,10 +2342,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721051.0124689142</v>
+        <v>721120</v>
       </c>
       <c r="R18" t="n">
-        <v>7146813.020376193</v>
+        <v>7146627</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2624,19 +2375,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2668,15 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>109909840</v>
+        <v>112610223</v>
       </c>
       <c r="B19" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,21 +2420,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2708,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720985.0293630471</v>
+        <v>721118</v>
       </c>
       <c r="R19" t="n">
-        <v>7146654.930285196</v>
+        <v>7146624</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2741,19 +2477,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2785,37 +2511,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>109909839</v>
+        <v>112606180</v>
       </c>
       <c r="B20" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57945</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>100110</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2825,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720958.7233230621</v>
+        <v>720995</v>
       </c>
       <c r="R20" t="n">
-        <v>7146663.888066227</v>
+        <v>7146912</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2858,19 +2579,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2902,37 +2613,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>109909838</v>
+        <v>112606168</v>
       </c>
       <c r="B21" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2942,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720911.3782035192</v>
+        <v>720869</v>
       </c>
       <c r="R21" t="n">
-        <v>7146620.94181836</v>
+        <v>7146632</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2975,19 +2681,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3019,37 +2715,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>109909836</v>
+        <v>112606170</v>
       </c>
       <c r="B22" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3059,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721095.0066429669</v>
+        <v>720939</v>
       </c>
       <c r="R22" t="n">
-        <v>7146589.47390327</v>
+        <v>7146565</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3092,19 +2783,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3136,37 +2817,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>109909837</v>
+        <v>112606176</v>
       </c>
       <c r="B23" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3176,10 +2852,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721096.6747428864</v>
+        <v>720996</v>
       </c>
       <c r="R23" t="n">
-        <v>7146590.46322284</v>
+        <v>7146704</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3209,19 +2885,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3253,37 +2919,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>109909835</v>
+        <v>112606179</v>
       </c>
       <c r="B24" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3293,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>721118.6220685059</v>
+        <v>720958</v>
       </c>
       <c r="R24" t="n">
-        <v>7146623.758135555</v>
+        <v>7146897</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3326,19 +2987,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3370,15 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112606180</v>
+        <v>112610229</v>
       </c>
       <c r="B25" t="n">
-        <v>56644</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3386,21 +3032,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100110</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3410,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720995</v>
+        <v>720992</v>
       </c>
       <c r="R25" t="n">
-        <v>7146912</v>
+        <v>7146705</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3480,16 +3126,11 @@
         <v>112606177</v>
       </c>
       <c r="B26" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3584,15 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112610224</v>
+        <v>112610230</v>
       </c>
       <c r="B27" t="n">
-        <v>77891</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,21 +3236,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>103031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3624,10 +3260,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721095</v>
+        <v>720972</v>
       </c>
       <c r="R27" t="n">
-        <v>7146589</v>
+        <v>7146771</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3688,648 +3324,6 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>112610223</v>
-      </c>
-      <c r="B28" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>721119</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7146624</v>
-      </c>
-      <c r="S28" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>112610230</v>
-      </c>
-      <c r="B29" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Perisoreus infaustus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>720972</v>
-      </c>
-      <c r="R29" t="n">
-        <v>7146771</v>
-      </c>
-      <c r="S29" t="n">
-        <v>10</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>112610226</v>
-      </c>
-      <c r="B30" t="n">
-        <v>77891</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>185</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Bryoria nadvornikiana</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>720911</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7146621</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>112610227</v>
-      </c>
-      <c r="B31" t="n">
-        <v>77608</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>720959</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7146664</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>112610229</v>
-      </c>
-      <c r="B32" t="n">
-        <v>5160</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>720991</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7146705</v>
-      </c>
-      <c r="S32" t="n">
-        <v>10</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>112610233</v>
-      </c>
-      <c r="B33" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>721051</v>
-      </c>
-      <c r="R33" t="n">
-        <v>7146813</v>
-      </c>
-      <c r="S33" t="n">
-        <v>10</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43261-2021 artfynd.xlsx
+++ b/artfynd/A 43261-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606166</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606169</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610224</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610226</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606164</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606171</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606174</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606181</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606182</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610228</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610231</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610233</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606173</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2100,6 +2170,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610227</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606167</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610225</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2406,6 +2491,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606165</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2508,6 +2598,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610223</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2610,6 +2705,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606180</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2712,6 +2812,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606168</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2814,6 +2919,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606170</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2916,6 +3026,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606176</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3018,6 +3133,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606179</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3120,6 +3240,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610229</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3222,6 +3347,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606177</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3324,8 +3454,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610230</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>